--- a/questionnaire_templates/008_monster_personality_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/008_monster_personality_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'brave'}</t>
+          <t>brave</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Brave'}</t>
+          <t>Brave</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fearless'}</t>
+          <t>fearless</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fearless'}</t>
+          <t>Fearless</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'courageous'}</t>
+          <t>courageous</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Courageous'}</t>
+          <t>Courageous</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'burger'}</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Burger'}</t>
+          <t>Burger</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pizza'}</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pizza'}</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'salad'}</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Salad'}</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hiking'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hiking'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'gaming'}</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Gaming'}</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
